--- a/Listing/SWAWR.xlsx
+++ b/Listing/SWAWR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="48">
   <si>
     <t/>
   </si>
@@ -55,49 +55,88 @@
     <t>3</t>
   </si>
   <si>
+    <t>20141375</t>
+  </si>
+  <si>
+    <t>CHOMP WHOOSS MLOW 50</t>
+  </si>
+  <si>
+    <t>20141452</t>
+  </si>
+  <si>
+    <t>CHMP COLORFUL MLW 50</t>
+  </si>
+  <si>
     <t>20109430</t>
   </si>
   <si>
     <t>CHOMP MLOW PLAIN 50G</t>
   </si>
   <si>
+    <t>20101907</t>
+  </si>
+  <si>
+    <t>CHOMP MLOW BURGER 50</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20092548</t>
+  </si>
+  <si>
+    <t>CHOMP DUCKIE MARSH50</t>
+  </si>
+  <si>
+    <t>20096157</t>
+  </si>
+  <si>
+    <t>CHOMP MLLOW STRW 50</t>
+  </si>
+  <si>
+    <t>20101460</t>
+  </si>
+  <si>
+    <t>CHOMP ICE.CRM STR 50</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20069650</t>
+  </si>
+  <si>
+    <t>CHOMP ICE.CRM BLU 50</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
     <t>20094168</t>
   </si>
   <si>
     <t>CHOMP2 TWIST MARS 50</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20092548</t>
-  </si>
-  <si>
-    <t>CHOMP DUCKIE MARSH50</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20101907</t>
-  </si>
-  <si>
-    <t>CHOMP MLOW BURGER 50</t>
-  </si>
-  <si>
     <t>20078838</t>
   </si>
   <si>
     <t>CHOMP GOLD.COIN 6'S</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20101460</t>
-  </si>
-  <si>
-    <t>CHOMP ICE.CRM STR 50</t>
+    <t>20064556</t>
+  </si>
+  <si>
+    <t>CHOMP2 TWISTER 50G</t>
+  </si>
+  <si>
+    <t>20137587</t>
+  </si>
+  <si>
+    <t>CHOMP2 MALLOWPOP 16G</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>20133216</t>
@@ -106,16 +145,7 @@
     <t>CHOMP TRIO PLAIN 21G</t>
   </si>
   <si>
-    <t>20064556</t>
-  </si>
-  <si>
-    <t>CHOMP2 TWISTER 50G</t>
-  </si>
-  <si>
-    <t>20069650</t>
-  </si>
-  <si>
-    <t>CHOMP ICE.CRM BLU 50</t>
+    <t>7</t>
   </si>
   <si>
     <t>20133246</t>
@@ -124,16 +154,7 @@
     <t>CHOMP TRIO RNBOW 21G</t>
   </si>
   <si>
-    <t>20096157</t>
-  </si>
-  <si>
-    <t>CHOMP MLLOW STRW 50</t>
-  </si>
-  <si>
-    <t>20137587</t>
-  </si>
-  <si>
-    <t>CHOMP2 MALLOWPOP 16G</t>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -526,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -673,24 +694,24 @@
         <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -698,19 +719,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -718,39 +739,39 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -758,16 +779,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>4</v>
@@ -778,22 +799,22 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -807,13 +828,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -827,13 +848,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -847,10 +868,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -867,12 +888,52 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
